--- a/Excel/TitleConfig.xlsx
+++ b/Excel/TitleConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AD8846-04D0-4363-980B-ED85E7776E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F41E9F-5FD6-4094-91B4-ED68726FF776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TitleProto" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="118">
   <si>
     <t>Id</t>
   </si>
@@ -320,6 +320,133 @@
   </si>
   <si>
     <t>100402;0.03@200103;0.03@203003;0.1@203103;0.1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Newbie of the Martial Arts</t>
+  </si>
+  <si>
+    <t>Nameless person</t>
+  </si>
+  <si>
+    <t>Famous throughout the land</t>
+  </si>
+  <si>
+    <t>Winged Hero</t>
+  </si>
+  <si>
+    <t>Heroic Hero</t>
+  </si>
+  <si>
+    <t>The mundane world has no rules.</t>
+  </si>
+  <si>
+    <t>Unstoppable Hero</t>
+  </si>
+  <si>
+    <t>Wu Lin Zhen Zong</t>
+  </si>
+  <si>
+    <t>Epic Hero</t>
+  </si>
+  <si>
+    <t>Desolate Victory</t>
+  </si>
+  <si>
+    <t>Nine Sky Vortex</t>
+  </si>
+  <si>
+    <t>The world laughs at my madness</t>
+  </si>
+  <si>
+    <t>One Blade Skyward</t>
+  </si>
+  <si>
+    <t>Blood volume + 300</t>
+  </si>
+  <si>
+    <t>Health + 500</t>
+  </si>
+  <si>
+    <t>Attack +10</t>
+  </si>
+  <si>
+    <t>Health increases by 1%</t>
+  </si>
+  <si>
+    <t>Attack +120</t>
+  </si>
+  <si>
+    <t>Attack increases by 1%</t>
+  </si>
+  <si>
+    <t>Damage bonus +2%</t>
+  </si>
+  <si>
+    <t>Critical hit rate + 2%</t>
+  </si>
+  <si>
+    <t>Increase critical hit rate by 3%</t>
+  </si>
+  <si>
+    <t>Attack + 600</t>
+  </si>
+  <si>
+    <t>Increases damage to Lord monsters by 10%</t>
+  </si>
+  <si>
+    <t>Increased evasion rate by 3%</t>
+  </si>
+  <si>
+    <t>Attack Increase 5%, Damage to Monsters +10%</t>
+  </si>
+  <si>
+    <t>Attack boost 3%, Critical Hit Rate +3%, Damage to Monsters +10%</t>
+  </si>
+  <si>
+    <t>Activate upon completing level 30 mission</t>
+  </si>
+  <si>
+    <t>Activate upon completing the task at level 60</t>
+  </si>
+  <si>
+    <t>Obtain Sponsorship Pack</t>
+  </si>
+  <si>
+    <t>Achievement system acquisition</t>
+  </si>
+  <si>
+    <t>It can be obtained by logging into the reward system</t>
+  </si>
+  <si>
+    <t>Battlefield activities acquisition</t>
+  </si>
+  <si>
+    <t>Arena event acquisition</t>
+  </si>
+  <si>
+    <t>Obtained through the Sign-in System</t>
+  </si>
+  <si>
+    <t>Obtained through token system</t>
+  </si>
+  <si>
+    <t>Points system acquisition</t>
+  </si>
+  <si>
+    <t>Des_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetDes_EN</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -424,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -434,6 +561,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -740,27 +870,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:V28"/>
+  <dimension ref="C1:Y28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="41.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="32.625" style="2" customWidth="1"/>
-    <col min="11" max="13" width="9" style="2"/>
-    <col min="14" max="14" width="18.75" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="4" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="41.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" customWidth="1"/>
+    <col min="11" max="12" width="32.625" style="2" customWidth="1"/>
+    <col min="13" max="15" width="9" style="2"/>
+    <col min="16" max="16" width="18.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="41.75" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -768,37 +909,46 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -806,37 +956,46 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q4" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
@@ -844,609 +1003,744 @@
         <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="3:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q5" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="3:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="4">
         <v>10001</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="4">
         <v>10001</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H6" s="4">
         <v>10001</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <v>10</v>
       </c>
-      <c r="I6" s="4">
+      <c r="J6" s="4">
         <v>-1</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="M6" s="4">
         <v>2</v>
       </c>
-      <c r="L6" s="4">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-    </row>
-    <row r="7" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+    </row>
+    <row r="7" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4">
         <v>10002</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="4">
         <v>10002</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="4">
         <v>10002</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <v>8</v>
       </c>
-      <c r="I7" s="4">
+      <c r="J7" s="4">
         <v>-1</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="K7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="M7" s="4">
         <v>2</v>
       </c>
-      <c r="L7" s="4">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="T7" s="1"/>
-      <c r="V7" s="1"/>
-    </row>
-    <row r="8" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="W7" s="1"/>
+      <c r="Y7" s="1"/>
+    </row>
+    <row r="8" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="4">
         <v>10003</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="4">
         <v>10003</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="4">
+      <c r="H8" s="4">
         <v>10008</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <v>10</v>
       </c>
-      <c r="I8" s="4">
+      <c r="J8" s="4">
         <v>-1</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8" s="4">
         <v>2</v>
       </c>
-      <c r="L8" s="4">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="T8" s="1"/>
-      <c r="V8" s="1"/>
-    </row>
-    <row r="9" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="W8" s="1"/>
+      <c r="Y8" s="1"/>
+    </row>
+    <row r="9" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="4">
         <v>10004</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="4">
         <v>10004</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="4">
+      <c r="H9" s="4">
         <v>10004</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <v>10</v>
       </c>
-      <c r="I9" s="4">
+      <c r="J9" s="4">
         <v>-1</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="K9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="4">
+      <c r="L9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M9" s="4">
         <v>2</v>
       </c>
-      <c r="L9" s="4">
-        <v>0</v>
-      </c>
-      <c r="M9" s="4">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="4">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="T9" s="1"/>
-      <c r="V9" s="1"/>
-    </row>
-    <row r="10" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="W9" s="1"/>
+      <c r="Y9" s="1"/>
+    </row>
+    <row r="10" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="4">
         <v>100041</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="4">
         <v>10016</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="4">
         <v>10016</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <v>10</v>
       </c>
-      <c r="I10" s="4">
+      <c r="J10" s="4">
         <v>-1</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="4">
+      <c r="L10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="4">
         <v>2</v>
       </c>
-      <c r="L10" s="4">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T10" s="1"/>
-      <c r="V10" s="1"/>
-    </row>
-    <row r="11" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="W10" s="1"/>
+      <c r="Y10" s="1"/>
+    </row>
+    <row r="11" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="4">
         <v>10005</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="4">
         <v>10005</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="4">
         <v>10005</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <v>10</v>
       </c>
-      <c r="I11" s="4">
+      <c r="J11" s="4">
         <v>-1</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K11" s="4">
+      <c r="L11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="4">
         <v>2</v>
       </c>
-      <c r="L11" s="4">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="T11" s="1"/>
-      <c r="V11" s="1"/>
-    </row>
-    <row r="12" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q11" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="W11" s="1"/>
+      <c r="Y11" s="1"/>
+    </row>
+    <row r="12" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="4">
         <v>10006</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="4">
         <v>10006</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="4">
+      <c r="H12" s="4">
         <v>10006</v>
       </c>
-      <c r="H12" s="4">
+      <c r="I12" s="4">
         <v>11</v>
       </c>
-      <c r="I12" s="4">
+      <c r="J12" s="4">
         <v>86400</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="K12" s="4">
+      <c r="L12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" s="4">
         <v>2</v>
       </c>
-      <c r="L12" s="4">
+      <c r="N12" s="4">
         <v>-25</v>
       </c>
-      <c r="M12" s="4">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="s">
+      <c r="O12" s="4">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="T12" s="1"/>
-      <c r="V12" s="1"/>
-    </row>
-    <row r="13" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q12" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="W12" s="1"/>
+      <c r="Y12" s="1"/>
+    </row>
+    <row r="13" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="4">
         <v>10007</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="4">
         <v>10007</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="4">
+      <c r="H13" s="4">
         <v>10007</v>
       </c>
-      <c r="H13" s="4">
+      <c r="I13" s="4">
         <v>11</v>
       </c>
-      <c r="I13" s="4">
+      <c r="J13" s="4">
         <v>86400</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="4">
+      <c r="L13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" s="4">
         <v>2</v>
       </c>
-      <c r="L13" s="4">
+      <c r="N13" s="4">
         <v>-25</v>
       </c>
-      <c r="M13" s="4">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="s">
+      <c r="O13" s="4">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="T13" s="1"/>
-      <c r="V13" s="1"/>
-    </row>
-    <row r="14" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q13" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="W13" s="1"/>
+      <c r="Y13" s="1"/>
+    </row>
+    <row r="14" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="4">
         <v>10008</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="4">
         <v>10008</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="4">
+      <c r="H14" s="4">
         <v>10003</v>
       </c>
-      <c r="H14" s="4">
+      <c r="I14" s="4">
         <v>11</v>
       </c>
-      <c r="I14" s="4">
+      <c r="J14" s="4">
         <v>-1</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="K14" s="4">
+      <c r="L14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M14" s="4">
         <v>2</v>
       </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="s">
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="T14" s="1"/>
-      <c r="V14" s="1"/>
-    </row>
-    <row r="15" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q14" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="W14" s="1"/>
+      <c r="Y14" s="1"/>
+    </row>
+    <row r="15" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="4">
         <v>10009</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="4">
         <v>10009</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="4">
+      <c r="H15" s="4">
         <v>10009</v>
       </c>
-      <c r="H15" s="4">
+      <c r="I15" s="4">
         <v>11</v>
       </c>
-      <c r="I15" s="4">
+      <c r="J15" s="4">
         <v>-1</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K15" s="4">
+      <c r="L15" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M15" s="4">
         <v>2</v>
       </c>
-      <c r="L15" s="4">
-        <v>0</v>
-      </c>
-      <c r="M15" s="4">
-        <v>0</v>
-      </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="T15" s="1"/>
-      <c r="V15" s="1"/>
-    </row>
-    <row r="16" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="W15" s="1"/>
+      <c r="Y15" s="1"/>
+    </row>
+    <row r="16" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="4">
         <v>10011</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="4">
         <v>10011</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="4">
+      <c r="H16" s="4">
         <v>10011</v>
       </c>
-      <c r="H16" s="4">
+      <c r="I16" s="4">
         <v>10</v>
       </c>
-      <c r="I16" s="4">
+      <c r="J16" s="4">
         <v>-1</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="K16" s="4">
+      <c r="L16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M16" s="4">
         <v>2</v>
       </c>
-      <c r="L16" s="4">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4">
-        <v>0</v>
-      </c>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="T16" s="1"/>
-      <c r="V16" s="1"/>
-    </row>
-    <row r="17" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q16" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="W16" s="1"/>
+      <c r="Y16" s="1"/>
+    </row>
+    <row r="17" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="4">
         <v>10013</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="4">
         <v>10013</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="4">
+      <c r="H17" s="4">
         <v>10013</v>
       </c>
-      <c r="H17" s="4">
+      <c r="I17" s="4">
         <v>11</v>
       </c>
-      <c r="I17" s="4">
+      <c r="J17" s="4">
         <v>-1</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="4">
+      <c r="L17" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M17" s="4">
         <v>2</v>
       </c>
-      <c r="L17" s="4">
-        <v>0</v>
-      </c>
-      <c r="M17" s="4">
-        <v>0</v>
-      </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="4">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="T17" s="1"/>
-      <c r="V17" s="1"/>
-    </row>
-    <row r="18" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q17" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="W17" s="1"/>
+      <c r="Y17" s="1"/>
+    </row>
+    <row r="18" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="4">
         <v>10014</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="4">
         <v>10014</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G18" s="4">
+      <c r="H18" s="4">
         <v>10014</v>
       </c>
-      <c r="H18" s="4">
+      <c r="I18" s="4">
         <v>9</v>
       </c>
-      <c r="I18" s="4">
+      <c r="J18" s="4">
         <v>-1</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="K18" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="K18" s="4">
+      <c r="L18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M18" s="4">
         <v>2</v>
       </c>
-      <c r="L18" s="4">
-        <v>0</v>
-      </c>
-      <c r="M18" s="4">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4" t="s">
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="T18" s="1"/>
-      <c r="V18" s="1"/>
-    </row>
-    <row r="19" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q18" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="W18" s="1"/>
+      <c r="Y18" s="1"/>
+    </row>
+    <row r="19" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="4">
         <v>10015</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="4">
         <v>10015</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G19" s="4">
+      <c r="H19" s="4">
         <v>10015</v>
       </c>
-      <c r="H19" s="4">
+      <c r="I19" s="4">
         <v>10</v>
       </c>
-      <c r="I19" s="4">
+      <c r="J19" s="4">
         <v>-1</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="K19" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="K19" s="4">
+      <c r="L19" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M19" s="4">
         <v>2</v>
       </c>
-      <c r="L19" s="4">
-        <v>0</v>
-      </c>
-      <c r="M19" s="4">
-        <v>0</v>
-      </c>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="4">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="T19" s="1"/>
-      <c r="V19" s="1"/>
-    </row>
-    <row r="20" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="T20" s="1"/>
-      <c r="V20" s="1"/>
-    </row>
-    <row r="21" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="3:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="Q19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="W19" s="1"/>
+      <c r="Y19" s="1"/>
+    </row>
+    <row r="20" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W20" s="1"/>
+      <c r="Y20" s="1"/>
+    </row>
+    <row r="21" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/TitleConfig.xlsx
+++ b/Excel/TitleConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F41E9F-5FD6-4094-91B4-ED68726FF776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D830CB61-887B-4B08-BD1C-262B5D0041CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -408,36 +408,6 @@
     <t>Attack boost 3%, Critical Hit Rate +3%, Damage to Monsters +10%</t>
   </si>
   <si>
-    <t>Activate upon completing level 30 mission</t>
-  </si>
-  <si>
-    <t>Activate upon completing the task at level 60</t>
-  </si>
-  <si>
-    <t>Obtain Sponsorship Pack</t>
-  </si>
-  <si>
-    <t>Achievement system acquisition</t>
-  </si>
-  <si>
-    <t>It can be obtained by logging into the reward system</t>
-  </si>
-  <si>
-    <t>Battlefield activities acquisition</t>
-  </si>
-  <si>
-    <t>Arena event acquisition</t>
-  </si>
-  <si>
-    <t>Obtained through the Sign-in System</t>
-  </si>
-  <si>
-    <t>Obtained through token system</t>
-  </si>
-  <si>
-    <t>Points system acquisition</t>
-  </si>
-  <si>
     <t>Des_EN</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -448,6 +418,36 @@
   <si>
     <t>c</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv30 Quest Activation</t>
+  </si>
+  <si>
+    <t>Lv60 Quest Activation</t>
+  </si>
+  <si>
+    <t>Sponsor Pack Acquisition</t>
+  </si>
+  <si>
+    <t>Achievement System Acquisition</t>
+  </si>
+  <si>
+    <t>Login Reward System Acquisition</t>
+  </si>
+  <si>
+    <t>Battlefield Event Acquisition</t>
+  </si>
+  <si>
+    <t>Arena Event Acquisition</t>
+  </si>
+  <si>
+    <t>Check-in System Acquisition</t>
+  </si>
+  <si>
+    <t>Token System Acquisition</t>
+  </si>
+  <si>
+    <t>Point System Acquisition</t>
   </si>
 </sst>
 </file>
@@ -563,7 +563,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -892,13 +892,13 @@
     <row r="1" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -977,7 +977,7 @@
         <v>17</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>18</v>
@@ -992,7 +992,7 @@
         <v>21</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1086,7 +1086,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -1136,7 +1136,7 @@
         <v>32</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="W7" s="1"/>
       <c r="Y7" s="1"/>
@@ -1185,7 +1185,7 @@
         <v>34</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="W8" s="1"/>
       <c r="Y8" s="1"/>
@@ -1234,7 +1234,7 @@
         <v>38</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="W9" s="1"/>
       <c r="Y9" s="1"/>
@@ -1283,7 +1283,7 @@
         <v>40</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="W10" s="1"/>
       <c r="Y10" s="1"/>
@@ -1332,7 +1332,7 @@
         <v>38</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="W11" s="1"/>
       <c r="Y11" s="1"/>
@@ -1381,7 +1381,7 @@
         <v>47</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="W12" s="1"/>
       <c r="Y12" s="1"/>
@@ -1430,7 +1430,7 @@
         <v>51</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="W13" s="1"/>
       <c r="Y13" s="1"/>
@@ -1479,7 +1479,7 @@
         <v>53</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="W14" s="1"/>
       <c r="Y14" s="1"/>
@@ -1528,7 +1528,7 @@
         <v>55</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="W15" s="1"/>
       <c r="Y15" s="1"/>
@@ -1577,7 +1577,7 @@
         <v>57</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="W16" s="1"/>
       <c r="Y16" s="1"/>
@@ -1626,7 +1626,7 @@
         <v>53</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="W17" s="1"/>
       <c r="Y17" s="1"/>
@@ -1675,7 +1675,7 @@
         <v>57</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="W18" s="1"/>
       <c r="Y18" s="1"/>
@@ -1724,7 +1724,7 @@
         <v>57</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="W19" s="1"/>
       <c r="Y19" s="1"/>
